--- a/SourceData/Datas/goto.xlsx
+++ b/SourceData/Datas/goto.xlsx
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8.54545454545454" customWidth="1" min="1" max="1"/>
@@ -1147,7 +1147,6 @@
           <t>None</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" t="n">
@@ -1205,7 +1204,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>作物成熟后，空手点击收获</t>
+          <t>把催熟剂拖到快捷栏使用，再空手收获</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1219,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>请选中鱼竿，走到湖边抛竿</t>
+          <t>先选鱼竿，跟着箭头走到西边码头抛竿</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1279,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>走到湖边或码头钓鱼</t>
+          <t>跟着箭头走到湖边码头，点击抛竿</t>
         </is>
       </c>
     </row>
@@ -1296,6 +1295,111 @@
       <c r="D16" t="inlineStr">
         <is>
           <t>走到工作台旁点击打开合成</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HintTownGate</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>跟着箭头走到北侧「通往小镇」路牌，点击前往</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>13</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>HintTownGate</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>跟着箭头走到北侧「通往小镇」路牌，点击前往</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>14</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>HintMayor</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>在小镇北区找到镇长府并点击拜访</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>15</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>走进任意商店，购买一件商品</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>16</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>前往警察局或邮局，接取公告板任务</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>17</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>前往东市木工坊，点击了解工匠</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>18</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>前往社区中心，查看修复工程</t>
         </is>
       </c>
     </row>

--- a/SourceData/Datas/goto.xlsx
+++ b/SourceData/Datas/goto.xlsx
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8.54545454545454" customWidth="1" min="1" max="1"/>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>请选中锄头，点击荒地开垦</t>
+          <t>打开背包，把锄头拖到快捷栏，再点击荒地开垦</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>请选中种子，点击翻好地块播种</t>
+          <t>打开背包，把种子拖到快捷栏，再点击翻好地块播种</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>请选中水壶，给作物浇水</t>
+          <t>打开背包，把水壶拖到快捷栏，再给作物浇水</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>先选鱼竿，跟着箭头走到西边码头抛竿</t>
+          <t>打开背包，把鱼竿拖到快捷栏，再走到西边码头抛竿</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>跟着箭头走到湖边码头，点击抛竿</t>
+          <t>打开背包，把鱼竿拖到快捷栏，再走到湖边码头抛竿</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>跟着箭头走到北侧「通往小镇」路牌，点击前往</t>
+          <t>跟着箭头走到东侧「通往小镇」路牌，点击前往</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>跟着箭头走到北侧「通往小镇」路牌，点击前往</t>
+          <t>跟着箭头走到东侧「通往小镇」路牌，点击前往</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>在小镇北区找到镇长府并点击拜访</t>
+          <t>往北走到镇长府，点大门进屋，再跟镇长·艾岚打招呼</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>走进任意商店，购买一件商品</t>
+          <t>前往警察局或邮局，接取公告板任务</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>前往警察局或邮局，接取公告板任务</t>
+          <t>前往东市木工坊，点击了解工匠</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>前往东市木工坊，点击了解工匠</t>
+          <t>前往社区中心，查看修复工程</t>
         </is>
       </c>
     </row>
@@ -1399,10 +1399,153 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>前往社区中心，查看修复工程</t>
-        </is>
-      </c>
-    </row>
+          <t>走进任意商店，购买一件商品</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>19</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>打开商店，点「出售」卖掉一件收获物</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>20</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>回到社区中心，在春厅收集包上签字</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>21</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>前往微光诊所，听取矿洞叮嘱</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>22</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>走进矿脉商会（矿石店），打听浅层矿洞</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>23</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>点击北山「通往浅层矿洞」路牌进入</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>24</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>选中锄头，点击铜矿石开采</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>25</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>带着铜矿回到社区中心，点亮春厅</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>26</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>HintRock</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>打开背包，把锄头拖到快捷栏，再点击石子或岩石挖取石料</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>27</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SelectAxe</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>打开背包，把斧头拖到快捷栏，再点击松树或橡树砍伐</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/SourceData/Datas/goto.xlsx
+++ b/SourceData/Datas/goto.xlsx
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8.54545454545454" customWidth="1" min="1" max="1"/>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>走进矿脉商会（矿石店），打听浅层矿洞</t>
+          <t>走进矿脉商会，向掌柜打听浅层矿洞放行</t>
         </is>
       </c>
     </row>
@@ -1538,14 +1538,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/SourceData/Datas/goto.xlsx
+++ b/SourceData/Datas/goto.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="18400" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="goto" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="goto" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="8.54545454545454" customWidth="1" min="1" max="1"/>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>把催熟剂拖到快捷栏使用，再空手收获</t>
+          <t>睡醒后空手点成熟作物收获。也可用催熟剂跳过一晚。</t>
         </is>
       </c>
     </row>
@@ -1535,6 +1535,21 @@
       <c r="D32" t="inlineStr">
         <is>
           <t>打开背包，把斧头拖到快捷栏，再点击松树或橡树砍伐</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>28</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>点小屋门，睡到明天</t>
         </is>
       </c>
     </row>
